--- a/StatPub/SummaryPub.xlsx
+++ b/StatPub/SummaryPub.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeremycarlot/Documents/Website/JayCrlt.github.io/StatPub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4FD609-64E1-7A49-A644-2E6A3DDC5D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C56994-88FB-FB44-9694-21EE15559E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2200" yWindow="660" windowWidth="28040" windowHeight="17400" xr2:uid="{AA7BDC4C-3198-3143-B6C5-3B280DE634B4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>pubid</t>
   </si>
@@ -188,6 +188,12 @@
   </si>
   <si>
     <t>QIV2ME_5wuYC</t>
+  </si>
+  <si>
+    <t>10.1002/oik.11371</t>
+  </si>
+  <si>
+    <t>WF5omc3nYNoC</t>
   </si>
 </sst>
 </file>
@@ -539,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E76F7CDC-2270-2A4C-873C-81EB6C9C0E5D}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" bestFit="1" customWidth="1"/>
@@ -851,18 +857,29 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>37</v>
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>36</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C25" t="s">
         <v>22</v>
       </c>
     </row>

--- a/StatPub/SummaryPub.xlsx
+++ b/StatPub/SummaryPub.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeremycarlot/Documents/Website/JayCrlt.github.io/StatPub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C56994-88FB-FB44-9694-21EE15559E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35502F45-531A-F349-A7A6-30C90F7FDC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2200" yWindow="660" windowWidth="28040" windowHeight="17400" xr2:uid="{AA7BDC4C-3198-3143-B6C5-3B280DE634B4}"/>
   </bookViews>
@@ -866,6 +866,9 @@
       <c r="C23" t="s">
         <v>51</v>
       </c>
+      <c r="D23">
+        <v>204056161</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
